--- a/2023/NEI/tables/Section-2/Hg-emissions.xlsx
+++ b/2023/NEI/tables/Section-2/Hg-emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/seltzer_karl_epa_gov1/Documents/Profile/Documents/GitHub/EIB-TSD_dev/2023/NEI/tables/Section-2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/seltzer_karl_epa_gov1/Documents/Documents/GitHub/EIB-TSD_dev/2023/NEI/tables/Section-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{2DD9D2DD-9371-4967-916F-8EB18BCEDA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC974D9F-A077-469C-8046-3BD2E9ACB315}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{2DD9D2DD-9371-4967-916F-8EB18BCEDA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9577CA9C-23F8-475A-B9ED-9A1B3D0895D4}"/>
   <bookViews>
-    <workbookView xWindow="-25065" yWindow="3195" windowWidth="22875" windowHeight="12990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="22485" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>S/L/T</t>
   </si>
   <si>
-    <t>State, local, tribal agency-submitted</t>
-  </si>
-  <si>
     <t>2023EPA_TRI</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>State, local, Tribal agency-submitted</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D2" s="4">
         <v>14.981</v>
@@ -629,10 +629,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="4">
         <v>3.89</v>
@@ -643,10 +643,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="4">
         <v>0.29699999999999999</v>
@@ -657,10 +657,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D5" s="4">
         <v>7.5999999999999998E-2</v>
@@ -671,10 +671,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="4">
         <v>1.6E-2</v>
@@ -685,10 +685,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D7" s="4">
         <v>3.0000000000000001E-5</v>
@@ -696,13 +696,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D8" s="4">
         <v>9.1649999999999991</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D9" s="4">
         <v>0.22800000000000001</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4">
         <v>0.20599999999999999</v>
@@ -738,13 +738,13 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D11" s="4">
         <v>1.7999999999999999E-2</v>
@@ -752,13 +752,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D12" s="4">
         <v>8.3999999999999995E-3</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D13" s="4">
         <v>0.35</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>4.1000000000000002E-2</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
